--- a/isms-core-framework/A.7-physical-controls/isms-a.7.10-storage-media/WKBK/90_workbooks/ISMS-IMP-A.7.10.3_Media_Lifecycle_Tracking_20260208.xlsx
+++ b/isms-core-framework/A.7-physical-controls/isms-a.7.10-storage-media/WKBK/90_workbooks/ISMS-IMP-A.7.10.3_Media_Lifecycle_Tracking_20260208.xlsx
@@ -1634,7 +1634,7 @@
       <formula1>"Yes,No,Unknown"</formula1>
     </dataValidation>
     <dataValidation sqref="R10:R100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"NIST 800-88 Clear,NIST 800-88 Purge,Cryptographic Erasure,Factory Reset,Full Format,Quick Format,Physical Destruction"</formula1>
+      <formula1>"NIST 800-88 Rev. 2 Clear,NIST 800-88 Rev. 2 Purge,Cryptographic Erasure,Factory Reset,Full Format,Quick Format,Physical Destruction"</formula1>
     </dataValidation>
     <dataValidation sqref="S10:S100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Full Verification,Sample Verification (10%),Log Review Only,None"</formula1>
